--- a/data/trans_dic/IP12B$abdomen-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$abdomen-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor abdominal</t>
+          <t>Menores que han limitado su actividad por síntomas o dolor abdominal (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,81</t>
+          <t>0,0; 36,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,85</t>
+          <t>0,0; 37,55</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,25</t>
+          <t>0,0; 13,3</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,41</t>
+          <t>0,0; 24,8</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,62</t>
+          <t>0,0; 38,89</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,45</t>
+          <t>0,0; 20,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 70,95</t>
+          <t>0,0; 61,01</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,45</t>
+          <t>0,0; 38,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,79</t>
+          <t>0,0; 38,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,21</t>
+          <t>0,0; 36,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,61</t>
+          <t>0,0; 21,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,18</t>
+          <t>0,0; 23,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0; 7,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,09</t>
+          <t>0,0; 13,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,71</t>
+          <t>0,0; 25,03</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0; 6,36</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,55</t>
+          <t>0,0; 20,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,05</t>
+          <t>0,0; 13,91</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 3,48</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,75</t>
+          <t>0,0; 11,47</t>
         </is>
       </c>
     </row>
@@ -1117,7 +1118,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1127,37 +1128,37 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 11,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0; 18,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,47</t>
+          <t>0,0; 12,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1227,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,09</t>
+          <t>0,0; 42,27</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,06</t>
+          <t>0,0; 35,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1337,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 13,45</t>
+          <t>1,49; 13,65</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,45</t>
+          <t>1,09; 9,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,23</t>
+          <t>0,0; 5,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,79</t>
+          <t>0,0; 10,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 5,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,92</t>
+          <t>0,0; 7,57</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 8,56</t>
+          <t>1,4; 9,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,58; 5,83</t>
+          <t>0,61; 5,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,77</t>
+          <t>0,0; 4,68</t>
         </is>
       </c>
     </row>
@@ -1404,4 +1405,1283 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que han limitado su actividad por síntomas o dolor abdominal (tasa de respuesta: 99,36%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>448</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>747</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2100</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3243</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1917</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3781</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2543</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 2534</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1307</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>659</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2661</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2891</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 2658</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4049</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3239</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>634</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>1334</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3247</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 2864</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3831</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3380</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4053</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4295</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>678</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2825</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 2812</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>0; 2705</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>0; 3332</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>2360</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>2084</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>687</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>3702</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>2730</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>1332</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>620; 5663</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>663; 5884</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0; 2809</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4733</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3271</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>0; 3476</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>1239; 7939</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>724; 6740</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>0; 4621</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP12B$abdomen-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$abdomen-Clase-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor abdominal (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor abdominal (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,51</t>
+          <t>0,0; 38,81</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,55</t>
+          <t>0,0; 34,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,3</t>
+          <t>0,0; 16,47</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,8</t>
+          <t>0,0; 24,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,89</t>
+          <t>0,0; 47,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,11</t>
+          <t>0,0; 20,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,01</t>
+          <t>0,0; 61,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,29</t>
+          <t>0,0; 41,68</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,7</t>
+          <t>0,0; 38,79</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,05</t>
+          <t>0,0; 35,39</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,05</t>
+          <t>0,0; 19,2</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,48</t>
+          <t>0,0; 25,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,94</t>
+          <t>0,0; 17,17</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,03</t>
+          <t>0,0; 24,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,03</t>
+          <t>0,0; 24,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,91</t>
+          <t>0,0; 15,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,47</t>
+          <t>0,0; 11,1</t>
         </is>
       </c>
     </row>
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,36</t>
+          <t>0,0; 23,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,96</t>
+          <t>0,0; 15,67</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,27</t>
+          <t>0,0; 43,32</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,81</t>
+          <t>0,0; 36,61</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,49; 13,65</t>
+          <t>1,52; 13,19</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,09; 9,7</t>
+          <t>1,08; 9,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,32</t>
+          <t>0,0; 6,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,13</t>
+          <t>0,0; 8,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,58</t>
+          <t>0,0; 6,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,57</t>
+          <t>0,0; 7,48</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,4; 9,0</t>
+          <t>1,48; 8,91</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 5,65</t>
+          <t>0,56; 5,77</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,68</t>
+          <t>0,0; 4,7</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que han limitado su actividad por síntomas o dolor abdominal (tasa de respuesta: 99,36%)</t>
+          <t>Menores que en las últimas 2 semanas han limitado su actividad por síntomas o dolor abdominal (tasa de respuesta: 99,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2100</t>
+          <t>0; 2232</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3243</t>
+          <t>0; 2966</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 1917</t>
+          <t>0; 2373</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3781</t>
+          <t>0; 3750</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 2543</t>
+          <t>0; 3108</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2534</t>
+          <t>0; 2520</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2661</t>
+          <t>0; 2662</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 2891</t>
+          <t>0; 3147</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1980,7 +1980,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2658</t>
+          <t>0; 2664</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4049</t>
+          <t>0; 3974</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 3239</t>
+          <t>0; 2954</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3247</t>
+          <t>0; 3535</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 2864</t>
+          <t>0; 3530</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3831</t>
+          <t>0; 3775</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 3380</t>
+          <t>0; 4135</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4053</t>
+          <t>0; 4431</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4295</t>
+          <t>0; 4153</t>
         </is>
       </c>
     </row>
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2825</t>
+          <t>0; 2841</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 2812</t>
+          <t>0; 3399</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2705</t>
+          <t>0; 2772</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3332</t>
+          <t>0; 3406</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>620; 5663</t>
+          <t>632; 5472</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>663; 5884</t>
+          <t>657; 5491</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2809</t>
+          <t>0; 3455</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4733</t>
+          <t>0; 4032</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3271</t>
+          <t>0; 3982</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3476</t>
+          <t>0; 3435</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1239; 7939</t>
+          <t>1304; 7859</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>724; 6740</t>
+          <t>666; 6889</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4621</t>
+          <t>0; 4639</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP12B$abdomen-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP12B$abdomen-Clase-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,27 +625,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>7,79%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,65%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,12 +678,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,81</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,34</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -693,12 +693,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 33,81</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 43,85</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,47</t>
+          <t>0,0; 13,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,59</t>
+          <t>0,0; 24,41</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,22 +735,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>9,37%</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 40,62</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,0</t>
+          <t>0,0; 21,45</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -845,27 +845,27 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>9,35%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>15,25%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>8,73%</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>9,35%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,04</t>
+          <t>0,0; 38,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,68</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,79</t>
+          <t>0,0; 70,95</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 38,45</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,39</t>
+          <t>0,0; 40,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,2</t>
+          <t>0,0; 21,61</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -965,22 +965,22 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>3,82%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4,58%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
           <t>3,34%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,82%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,57</t>
+          <t>0,0; 22,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1018,12 +1018,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,17</t>
+          <t>0,0; 16,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,67</t>
+          <t>0,0; 20,18</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1033,12 +1033,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,5</t>
+          <t>0,0; 17,09</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,21</t>
+          <t>0,0; 16,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1048,7 +1048,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,1</t>
+          <t>0,0; 12,75</t>
         </is>
       </c>
     </row>
@@ -1070,22 +1070,22 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>5,61%</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,49</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1138,7 +1138,7 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 23,36</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1153,7 +1153,7 @@
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,67</t>
+          <t>0,0; 16,47</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1233,7 +1233,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 45,09</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1248,7 +1248,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,61</t>
+          <t>0,0; 29,06</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1285,32 +1285,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>2,87%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>5,69%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>3,43%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>1,3%</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2,87%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,52; 13,19</t>
+          <t>0,0; 8,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,08; 9,05</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,54</t>
+          <t>0,0; 6,92</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,63</t>
+          <t>1,52; 13,45</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,79</t>
+          <t>1,08; 9,45</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,48</t>
+          <t>0,0; 6,23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,48; 8,91</t>
+          <t>1,49; 8,56</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,56; 5,77</t>
+          <t>0,58; 5,83</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,7</t>
+          <t>0,0; 4,77</t>
         </is>
       </c>
     </row>
@@ -1438,14 +1438,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1533,27 +1533,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1586,27 +1586,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>448</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>747</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1639,12 +1639,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 2232</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2966</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -1654,12 +1654,12 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 1945</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3787</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 2373</t>
+          <t>0; 1909</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 3750</t>
+          <t>0; 3722</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1749,22 +1749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>613</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1802,7 +1802,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3108</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2656</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1832,7 +1832,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2520</t>
+          <t>0; 2703</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1864,22 +1864,22 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1912,27 +1912,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>665</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>659</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>642</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1965,12 +1965,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 2662</t>
+          <t>0; 2664</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3147</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1980,12 +1980,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0; 2664</t>
+          <t>0; 3095</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2903</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 3974</t>
+          <t>0; 4516</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 2954</t>
+          <t>0; 3326</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2075,32 +2075,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>700</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>634</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>687</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>700</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2128,7 +2128,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3535</t>
+          <t>0; 3475</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -2138,12 +2138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 3530</t>
+          <t>0; 2793</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3775</t>
+          <t>0; 2790</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2153,12 +2153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 4135</t>
+          <t>0; 3512</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 4431</t>
+          <t>0; 4676</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2168,7 +2168,7 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 4153</t>
+          <t>0; 4772</t>
         </is>
       </c>
     </row>
@@ -2190,22 +2190,22 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>678</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2841</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2825</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -2326,7 +2326,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 3399</t>
+          <t>0; 3573</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -2353,7 +2353,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -2406,7 +2406,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>645</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2886</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 2772</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -2489,7 +2489,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>0; 3406</t>
+          <t>0; 2704</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -2511,27 +2511,27 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2564,32 +2564,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>645</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>644</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
           <t>2360</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr">
         <is>
           <t>2084</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>687</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1342</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>645</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>644</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2617,47 +2617,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>632; 5472</t>
+          <t>0; 4107</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>657; 5491</t>
+          <t>0; 2800</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 3455</t>
+          <t>0; 3178</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 4032</t>
+          <t>630; 5581</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 3982</t>
+          <t>657; 5733</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 3435</t>
+          <t>0; 3292</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>1304; 7859</t>
+          <t>1315; 7551</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>666; 6889</t>
+          <t>686; 6960</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 4639</t>
+          <t>0; 4711</t>
         </is>
       </c>
     </row>
